--- a/public/exports-with-coowners/44023911.xlsx
+++ b/public/exports-with-coowners/44023911.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218776</t>
+          <t xml:space="preserve">311218780</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289447</t>
+          <t xml:space="preserve">311289501</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289447</t>
+          <t xml:space="preserve">311289501</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289447</t>
+          <t xml:space="preserve">311289501</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">

--- a/public/exports-with-coowners/44023911.xlsx
+++ b/public/exports-with-coowners/44023911.xlsx
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289501</t>
+          <t xml:space="preserve">311289447</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289501</t>
+          <t xml:space="preserve">311289447</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289501</t>
+          <t xml:space="preserve">311289447</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">

--- a/public/exports-with-coowners/44023911.xlsx
+++ b/public/exports-with-coowners/44023911.xlsx
@@ -3814,7 +3814,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218780</t>
+          <t xml:space="preserve">311218776</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
